--- a/Employee_Reports_wi52/Mohamed Nasardeen Mohamadu Main Q0436.xlsx
+++ b/Employee_Reports_wi52/Mohamed Nasardeen Mohamadu Main Q0436.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-77</v>
+        <v>-85</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1314,11 +1314,11 @@
         </is>
       </c>
       <c r="H18" s="5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
@@ -1363,11 +1363,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1412,11 +1412,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-162</v>
+        <v>-170</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-162</v>
+        <v>-170</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1694,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-21</v>
+        <v>-29</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1743,11 +1743,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-19</v>
+        <v>-27</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1780,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-23</v>
+        <v>-31</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1817,11 +1817,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1866,11 +1866,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1915,11 +1915,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -1964,11 +1964,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1979,41 +1979,41 @@
       <c r="K32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr"/>
-      <c r="D33" s="5" t="inlineStr"/>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>25-Aug-2024</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>25-Aug-2026</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr"/>
+      <c r="D33" s="3" t="inlineStr"/>
+      <c r="E33" s="3" t="inlineStr"/>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>26-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>25-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>728</v>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2525,7 +2525,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7901</v>
+        <v>7893</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7947</v>
+        <v>7939</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7954</v>
+        <v>7946</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7951</v>
+        <v>7943</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7955</v>
+        <v>7947</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
